--- a/data/reference/ttd_atual.xlsx
+++ b/data/reference/ttd_atual.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udesc-my.sharepoint.com/personal/06376528945_udesc_br/Documents/Arquivo Permanente/sri_udesc_cct/data/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="13_ncr:1_{869A146A-C7DC-473C-A5D6-2E76D52F5DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71BCE243-2577-43C3-9CAE-F857A49D5A5B}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="13_ncr:1_{869A146A-C7DC-473C-A5D6-2E76D52F5DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E509DD3-CE11-4B94-B546-065DA1594DAE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19AB5869-3503-4E3D-9A0C-F53498F9D468}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Atual" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$C$1:$C$714</definedName>
-    <definedName name="_Hlk109296914" localSheetId="0">Planilha1!#REF!</definedName>
-    <definedName name="_Hlk109297048" localSheetId="0">Planilha1!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Atual!$C$1:$C$714</definedName>
+    <definedName name="_Hlk109296914" localSheetId="0">Atual!#REF!</definedName>
+    <definedName name="_Hlk109297048" localSheetId="0">Atual!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -12527,7 +12527,7 @@
       <c r="I235" s="29"/>
       <c r="J235" s="29"/>
     </row>
-    <row r="236" spans="1:10" ht="48" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A236" s="37" t="s">
         <v>115</v>
       </c>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="J378" s="63"/>
     </row>
-    <row r="379" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A379" s="37" t="s">
         <v>322</v>
       </c>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="J379" s="63"/>
     </row>
-    <row r="380" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A380" s="37" t="s">
         <v>322</v>
       </c>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="J380" s="63"/>
     </row>
-    <row r="381" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A381" s="37" t="s">
         <v>322</v>
       </c>
@@ -15964,7 +15964,7 @@
       </c>
       <c r="J381" s="63"/>
     </row>
-    <row r="382" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A382" s="37" t="s">
         <v>322</v>
       </c>
@@ -16036,7 +16036,7 @@
       </c>
       <c r="J384" s="63"/>
     </row>
-    <row r="385" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A385" s="37" t="s">
         <v>322</v>
       </c>
@@ -16058,7 +16058,7 @@
       <c r="I385" s="70"/>
       <c r="J385" s="63"/>
     </row>
-    <row r="386" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A386" s="37" t="s">
         <v>322</v>
       </c>
@@ -16080,7 +16080,7 @@
       <c r="I386" s="70"/>
       <c r="J386" s="63"/>
     </row>
-    <row r="387" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A387" s="37" t="s">
         <v>322</v>
       </c>
@@ -16126,7 +16126,7 @@
       </c>
       <c r="J388" s="63"/>
     </row>
-    <row r="389" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A389" s="37" t="s">
         <v>322</v>
       </c>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="J389" s="63"/>
     </row>
-    <row r="390" spans="1:10" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" s="3" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A390" s="37" t="s">
         <v>322</v>
       </c>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="J390" s="109"/>
     </row>
-    <row r="391" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A391" s="37" t="s">
         <v>322</v>
       </c>
@@ -16196,7 +16196,7 @@
       <c r="I391" s="63"/>
       <c r="J391" s="63"/>
     </row>
-    <row r="392" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A392" s="37" t="s">
         <v>322</v>
       </c>
@@ -16218,7 +16218,7 @@
       <c r="I392" s="63"/>
       <c r="J392" s="63"/>
     </row>
-    <row r="393" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A393" s="37" t="s">
         <v>322</v>
       </c>
@@ -16244,7 +16244,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="394" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A394" s="37" t="s">
         <v>322</v>
       </c>
@@ -16268,7 +16268,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="395" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A395" s="37" t="s">
         <v>322</v>
       </c>
@@ -16292,7 +16292,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="396" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A396" s="37" t="s">
         <v>322</v>
       </c>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="J418" s="29"/>
     </row>
-    <row r="419" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A419" s="37" t="s">
         <v>366</v>
       </c>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="J420" s="29"/>
     </row>
-    <row r="421" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A421" s="37" t="s">
         <v>366</v>
       </c>
@@ -16892,7 +16892,7 @@
       </c>
       <c r="J421" s="29"/>
     </row>
-    <row r="422" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A422" s="37" t="s">
         <v>366</v>
       </c>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="J422" s="29"/>
     </row>
-    <row r="423" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A423" s="37" t="s">
         <v>366</v>
       </c>
@@ -16940,7 +16940,7 @@
       <c r="I423" s="30"/>
       <c r="J423" s="76"/>
     </row>
-    <row r="424" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A424" s="37" t="s">
         <v>366</v>
       </c>
@@ -16962,7 +16962,7 @@
       <c r="I424" s="29"/>
       <c r="J424" s="76"/>
     </row>
-    <row r="425" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A425" s="37" t="s">
         <v>366</v>
       </c>
@@ -16984,7 +16984,7 @@
       <c r="I425" s="29"/>
       <c r="J425" s="76"/>
     </row>
-    <row r="426" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A426" s="37" t="s">
         <v>366</v>
       </c>
@@ -17006,7 +17006,7 @@
       <c r="I426" s="29"/>
       <c r="J426" s="76"/>
     </row>
-    <row r="427" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A427" s="37" t="s">
         <v>366</v>
       </c>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="J427" s="29"/>
     </row>
-    <row r="428" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A428" s="37" t="s">
         <v>366</v>
       </c>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="J429" s="29"/>
     </row>
-    <row r="430" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A430" s="37" t="s">
         <v>366</v>
       </c>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="J430" s="29"/>
     </row>
-    <row r="431" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A431" s="37" t="s">
         <v>366</v>
       </c>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="J431" s="29"/>
     </row>
-    <row r="432" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A432" s="37" t="s">
         <v>366</v>
       </c>
@@ -17150,7 +17150,7 @@
       </c>
       <c r="J432" s="29"/>
     </row>
-    <row r="433" spans="1:10" ht="96" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" ht="84" x14ac:dyDescent="0.25">
       <c r="A433" s="37" t="s">
         <v>366</v>
       </c>
@@ -17174,7 +17174,7 @@
       <c r="I433" s="29"/>
       <c r="J433" s="29"/>
     </row>
-    <row r="434" spans="1:10" s="8" customFormat="1" ht="96" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" s="8" customFormat="1" ht="84" x14ac:dyDescent="0.25">
       <c r="A434" s="37" t="s">
         <v>366</v>
       </c>
@@ -17200,7 +17200,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="435" spans="1:10" s="8" customFormat="1" ht="96" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" s="8" customFormat="1" ht="84" x14ac:dyDescent="0.25">
       <c r="A435" s="37" t="s">
         <v>366</v>
       </c>
@@ -17226,7 +17226,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="436" spans="1:10" s="13" customFormat="1" ht="96" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" s="13" customFormat="1" ht="84" x14ac:dyDescent="0.25">
       <c r="A436" s="37" t="s">
         <v>366</v>
       </c>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="J440" s="29"/>
     </row>
-    <row r="441" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A441" s="37" t="s">
         <v>366</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="442" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A442" s="37" t="s">
         <v>366</v>
       </c>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="J442" s="29"/>
     </row>
-    <row r="443" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A443" s="37" t="s">
         <v>366</v>
       </c>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="J445" s="43"/>
     </row>
-    <row r="446" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A446" s="37" t="s">
         <v>366</v>
       </c>
@@ -17546,7 +17546,7 @@
       </c>
       <c r="J448" s="29"/>
     </row>
-    <row r="449" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A449" s="37" t="s">
         <v>366</v>
       </c>
@@ -17592,7 +17592,7 @@
       <c r="I450" s="29"/>
       <c r="J450" s="76"/>
     </row>
-    <row r="451" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A451" s="37" t="s">
         <v>366</v>
       </c>
@@ -17618,7 +17618,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="452" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A452" s="37" t="s">
         <v>366</v>
       </c>
@@ -17640,7 +17640,7 @@
       <c r="I452" s="29"/>
       <c r="J452" s="29"/>
     </row>
-    <row r="453" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A453" s="37" t="s">
         <v>366</v>
       </c>
@@ -17666,7 +17666,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="454" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A454" s="37" t="s">
         <v>366</v>
       </c>
@@ -17688,7 +17688,7 @@
       <c r="I454" s="29"/>
       <c r="J454" s="29"/>
     </row>
-    <row r="455" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A455" s="37" t="s">
         <v>366</v>
       </c>
@@ -17710,7 +17710,7 @@
       <c r="I455" s="29"/>
       <c r="J455" s="76"/>
     </row>
-    <row r="456" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A456" s="37" t="s">
         <v>366</v>
       </c>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="J456" s="76"/>
     </row>
-    <row r="457" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A457" s="37" t="s">
         <v>366</v>
       </c>
@@ -17780,7 +17780,7 @@
       <c r="I458" s="56"/>
       <c r="J458" s="76"/>
     </row>
-    <row r="459" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A459" s="37" t="s">
         <v>366</v>
       </c>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="J461" s="29"/>
     </row>
-    <row r="462" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A462" s="37" t="s">
         <v>366</v>
       </c>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="J463" s="43"/>
     </row>
-    <row r="464" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A464" s="37" t="s">
         <v>366</v>
       </c>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="J467" s="43"/>
     </row>
-    <row r="468" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A468" s="37" t="s">
         <v>366</v>
       </c>
@@ -18038,7 +18038,7 @@
       <c r="I469" s="43"/>
       <c r="J469" s="43"/>
     </row>
-    <row r="470" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A470" s="37" t="s">
         <v>366</v>
       </c>
@@ -18062,7 +18062,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="471" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A471" s="37" t="s">
         <v>366</v>
       </c>
@@ -18086,7 +18086,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="472" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A472" s="37" t="s">
         <v>366</v>
       </c>
@@ -18110,7 +18110,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="473" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A473" s="37" t="s">
         <v>366</v>
       </c>
@@ -18134,7 +18134,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="474" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A474" s="37" t="s">
         <v>366</v>
       </c>
@@ -18160,7 +18160,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="475" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A475" s="37" t="s">
         <v>366</v>
       </c>
@@ -18186,7 +18186,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="476" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A476" s="37" t="s">
         <v>366</v>
       </c>
@@ -18214,7 +18214,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="477" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A477" s="37" t="s">
         <v>366</v>
       </c>
@@ -18266,7 +18266,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="479" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A479" s="37" t="s">
         <v>366</v>
       </c>
@@ -18294,7 +18294,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="480" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A480" s="37" t="s">
         <v>366</v>
       </c>
@@ -18320,7 +18320,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="481" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A481" s="37" t="s">
         <v>366</v>
       </c>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="J544" s="29"/>
     </row>
-    <row r="545" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A545" s="37" t="s">
         <v>472</v>
       </c>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="J545" s="29"/>
     </row>
-    <row r="546" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A546" s="37" t="s">
         <v>472</v>
       </c>
@@ -19882,7 +19882,7 @@
       <c r="I547" s="29"/>
       <c r="J547" s="29"/>
     </row>
-    <row r="548" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A548" s="37" t="s">
         <v>472</v>
       </c>
@@ -19910,7 +19910,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="549" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A549" s="37" t="s">
         <v>472</v>
       </c>
@@ -19934,7 +19934,7 @@
       </c>
       <c r="J549" s="29"/>
     </row>
-    <row r="550" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A550" s="37" t="s">
         <v>472</v>
       </c>
@@ -19956,7 +19956,7 @@
       <c r="I550" s="56"/>
       <c r="J550" s="76"/>
     </row>
-    <row r="551" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A551" s="37" t="s">
         <v>472</v>
       </c>
@@ -19978,7 +19978,7 @@
       <c r="I551" s="56"/>
       <c r="J551" s="76"/>
     </row>
-    <row r="552" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A552" s="37" t="s">
         <v>472</v>
       </c>
@@ -20002,7 +20002,7 @@
       <c r="I552" s="29"/>
       <c r="J552" s="29"/>
     </row>
-    <row r="553" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A553" s="37" t="s">
         <v>472</v>
       </c>
@@ -20026,7 +20026,7 @@
       <c r="I553" s="29"/>
       <c r="J553" s="29"/>
     </row>
-    <row r="554" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A554" s="37" t="s">
         <v>472</v>
       </c>
@@ -20072,7 +20072,7 @@
       <c r="I555" s="30"/>
       <c r="J555" s="29"/>
     </row>
-    <row r="556" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A556" s="37" t="s">
         <v>472</v>
       </c>
@@ -20094,7 +20094,7 @@
       <c r="I556" s="29"/>
       <c r="J556" s="29"/>
     </row>
-    <row r="557" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A557" s="37" t="s">
         <v>472</v>
       </c>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="J557" s="29"/>
     </row>
-    <row r="558" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A558" s="37" t="s">
         <v>472</v>
       </c>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="J558" s="43"/>
     </row>
-    <row r="559" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A559" s="37" t="s">
         <v>472</v>
       </c>
@@ -20166,7 +20166,7 @@
       <c r="I559" s="29"/>
       <c r="J559" s="29"/>
     </row>
-    <row r="560" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A560" s="37" t="s">
         <v>472</v>
       </c>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="J560" s="29"/>
     </row>
-    <row r="561" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A561" s="37" t="s">
         <v>472</v>
       </c>
@@ -20214,7 +20214,7 @@
       <c r="I561" s="43"/>
       <c r="J561" s="29"/>
     </row>
-    <row r="562" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A562" s="37" t="s">
         <v>472</v>
       </c>
